--- a/CAPSTONE/bus311-capstone-valuation-model.xlsx
+++ b/CAPSTONE/bus311-capstone-valuation-model.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" r:id="Rd8e3d686f7a643a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Handoff" sheetId="2" r:id="R2eee89f2b29842fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs &amp; Sources" sheetId="3" r:id="Rd472cae5c8684fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Forecasts" sheetId="4" r:id="Ra187b3e21f4e400d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" r:id="R8226a8096824428b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Economics" sheetId="6" r:id="Rdbe3e104398744b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivities" sheetId="7" r:id="R7ba717b8c5504f5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Board Appendix" sheetId="8" r:id="R5a8ca62df0f14431"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" r:id="Ra470fd3bd1364f98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R2b9eaa9218a34f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" r:id="R194990601f834b0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Handoff" sheetId="2" r:id="R612c325817334267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs &amp; Sources" sheetId="3" r:id="Rfd5d3bbb8e2842ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Forecasts" sheetId="4" r:id="R1b2a86ae8f3a4ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" r:id="R6948c65c373941ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Economics" sheetId="6" r:id="Rf309cc1ab24f4abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivities" sheetId="7" r:id="Rfe9a3e2980e24938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Board Appendix" sheetId="8" r:id="R3d85cf2d96e1455e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" r:id="R7c9546b08ff2470f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="Rf1de07be335945bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -531,7 +531,7 @@
         <x:color rgb="FF19733B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F5EC"/>
         </x:patternFill>
       </x:fill>
@@ -542,7 +542,7 @@
         <x:color rgb="FFA32626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -553,7 +553,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4CC"/>
         </x:patternFill>
       </x:fill>
@@ -564,7 +564,7 @@
         <x:color rgb="FFC66A3D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E9E2"/>
         </x:patternFill>
       </x:fill>
@@ -594,6 +594,7 @@
     <c:plotArea>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -700,9 +701,6 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -840,9 +838,6 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -911,7 +906,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0ad1dd358ecb4852"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdf8406c7cc0f4092"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -941,7 +936,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R589a4d64e28744dc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R27ce8f3f170d4ba5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1712,7 +1707,7 @@
         <x:v>Scenario outputs, sensitivity, trigger, takeaway, and limitation</x:v>
       </x:c>
       <x:c r="D29" s="21" t="str">
-        <x:v>Useful CFO/Board evidence and Q&amp;A readiness</x:v>
+        <x:v>Useful CFO/Board evidence and oral-presentation readiness</x:v>
       </x:c>
       <x:c r="E29" s="73"/>
       <x:c r="F29" s="76" t="str">
@@ -3774,7 +3769,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03ee83c4379f4d51"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra046855ee2024965"/>
 </x:worksheet>
 </file>
 
@@ -6851,8 +6846,9 @@
       <x:c r="A17" s="21" t="str">
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="B17" s="53" t="str">
+      <x:c r="B17" s="53" t="n">
         <x:f>'Scenario Forecasts'!D7</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="53" t="n">
         <x:f>'Scenario Forecasts'!H9</x:f>
@@ -6861,8 +6857,9 @@
       <x:c r="D17" s="57" t="str">
         <x:f>'Valuation'!C14</x:f>
       </x:c>
-      <x:c r="E17" s="57" t="str">
+      <x:c r="E17" s="57" t="n">
         <x:f>'Valuation'!C15</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="53" t="n">
         <x:f>'Valuation'!C16</x:f>
@@ -6876,8 +6873,9 @@
       <x:c r="A18" s="21" t="str">
         <x:v>Upside</x:v>
       </x:c>
-      <x:c r="B18" s="53" t="str">
+      <x:c r="B18" s="53" t="n">
         <x:f>'Scenario Forecasts'!D30</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="53" t="n">
         <x:f>'Scenario Forecasts'!H32</x:f>
@@ -6886,8 +6884,9 @@
       <x:c r="D18" s="57" t="str">
         <x:f>'Valuation'!D14</x:f>
       </x:c>
-      <x:c r="E18" s="57" t="str">
+      <x:c r="E18" s="57" t="n">
         <x:f>'Valuation'!D15</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="53" t="n">
         <x:f>'Valuation'!D16</x:f>
@@ -6901,8 +6900,9 @@
       <x:c r="A19" s="21" t="str">
         <x:v>Downside</x:v>
       </x:c>
-      <x:c r="B19" s="53" t="str">
+      <x:c r="B19" s="53" t="n">
         <x:f>'Scenario Forecasts'!D53</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="53" t="n">
         <x:f>'Scenario Forecasts'!H55</x:f>
@@ -6978,7 +6978,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="71" t="str">
-        <x:v>Model-linked outputs and visuals designed for the PPTX appendix and individual Q&amp;A defense.</x:v>
+        <x:v>Model-linked outputs and visuals designed for the PowerPoint appendix and live-question support during the oral Board presentation.</x:v>
       </x:c>
       <x:c r="B2" s="71"/>
       <x:c r="C2" s="71"/>
@@ -7981,7 +7981,7 @@
     <x:mergeCell ref="B49:O49"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76aa25dea21f4c73"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5368eab2efea4444"/>
 </x:worksheet>
 </file>
 

--- a/CAPSTONE/bus311-capstone-valuation-model.xlsx
+++ b/CAPSTONE/bus311-capstone-valuation-model.xlsx
@@ -461,7 +461,7 @@
     <t>Scenario outputs, sensitivity, trigger, takeaway, and limitation</t>
   </si>
   <si>
-    <t>Useful CFO/Board evidence and oral-presentation readiness</t>
+    <t>Useful CFO/Board evidence and Oral Presentation readiness</t>
   </si>
   <si>
     <t>The Excel model is graded here as a working milestone; selected outputs belong in the final PPTX appendix.</t>
@@ -1235,7 +1235,7 @@
     <t>BUS311 Capstone Milestone 3 | Board Appendix</t>
   </si>
   <si>
-    <t>Model-linked outputs and visuals designed for the PowerPoint appendix and live-question support during the oral Board presentation.</t>
+    <t>Model-linked outputs and visuals designed for the PowerPoint appendix and live-question support during the Oral Presentation.</t>
   </si>
   <si>
     <t>Scenario valuation and operating evidence</t>
